--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,62 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54866993</v>
+        <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gärde, Djupmyren / S /, Jmt</t>
+          <t>myr, Torptjärnen, Sunne, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473593</v>
+        <v>473570</v>
       </c>
       <c r="R2" t="n">
-        <v>6997876</v>
+        <v>6997850</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,57 +752,48 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>14 skott inom 1 m2 i fuktig skog</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig skog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Axel Månsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Axel Månsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54866993</t>
+          <t>https://artportalen.se/Sighting/137089664</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54866994</v>
+        <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,51 +801,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gärde, Djupmyren / S /, Jmt</t>
+          <t>myr, Torptjärnen, Sunne, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473540</v>
+        <v>473570</v>
       </c>
       <c r="R3" t="n">
-        <v>6997781</v>
+        <v>6997850</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,92 +862,97 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>13 skott inom 1 m2 i fuktig skog</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>fuktig skog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Axel Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Axel Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54866994</t>
+          <t>https://artportalen.se/Sighting/137089697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54934487</v>
+        <v>54866993</v>
       </c>
       <c r="B4" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gärde, Djupmyren / S /, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473540</v>
+        <v>473593</v>
       </c>
       <c r="R4" t="n">
-        <v>6997781</v>
+        <v>6997876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I fuktig skog</t>
+          <t>14 skott inom 1 m2 i fuktig skog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,6 +1019,244 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54866993</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>54866994</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gärde, Djupmyren / S /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>473540</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6997781</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>13 skott inom 1 m2 i fuktig skog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>fuktig skog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54866994</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>54934487</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gärde, Djupmyren / S /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>473540</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6997781</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I fuktig skog</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>fuktig skog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54934487</t>
         </is>
@@ -1047,6 +1267,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137089664</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137089697</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
